--- a/artfynd/A 41396-2023 artfynd.xlsx
+++ b/artfynd/A 41396-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41396-2023 artfynd.xlsx
+++ b/artfynd/A 41396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112507903</v>
+        <v>112507507</v>
       </c>
       <c r="B2" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740215</v>
+        <v>740330</v>
       </c>
       <c r="R2" t="n">
-        <v>7417012</v>
+        <v>7416927</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112507534</v>
+        <v>112507488</v>
       </c>
       <c r="B3" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740128</v>
+        <v>740480</v>
       </c>
       <c r="R3" t="n">
-        <v>7417067</v>
+        <v>7417298</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112507533</v>
+        <v>112507527</v>
       </c>
       <c r="B4" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740235</v>
+        <v>740544</v>
       </c>
       <c r="R4" t="n">
-        <v>7416978</v>
+        <v>7417186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112507847</v>
+        <v>112507901</v>
       </c>
       <c r="B5" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740254</v>
+        <v>740539</v>
       </c>
       <c r="R5" t="n">
-        <v>7416908</v>
+        <v>7417180</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112507895</v>
+        <v>112507532</v>
       </c>
       <c r="B6" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740295</v>
+        <v>740544</v>
       </c>
       <c r="R6" t="n">
-        <v>7416878</v>
+        <v>7417186</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,31 +1148,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112507536</v>
+        <v>112507533</v>
       </c>
       <c r="B7" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1230,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740027</v>
+        <v>740235</v>
       </c>
       <c r="R7" t="n">
-        <v>7417179</v>
+        <v>7416979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112507876</v>
+        <v>112507534</v>
       </c>
       <c r="B8" t="n">
-        <v>95817</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740259</v>
+        <v>740128</v>
       </c>
       <c r="R8" t="n">
-        <v>7416868</v>
+        <v>7417067</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,44 +1342,39 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112507912</v>
+        <v>112507535</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1434,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740251</v>
+        <v>740052</v>
       </c>
       <c r="R9" t="n">
-        <v>7416872</v>
+        <v>7417140</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112507901</v>
+        <v>112507536</v>
       </c>
       <c r="B10" t="n">
-        <v>90608</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>740539</v>
+        <v>740027</v>
       </c>
       <c r="R10" t="n">
-        <v>7417181</v>
+        <v>7417179</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,49 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112507875</v>
+        <v>112507902</v>
       </c>
       <c r="B11" t="n">
-        <v>95817</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>740539</v>
+        <v>740474</v>
       </c>
       <c r="R11" t="n">
-        <v>7417227</v>
+        <v>7417081</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112507845</v>
+        <v>112507903</v>
       </c>
       <c r="B12" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>740052</v>
+        <v>740215</v>
       </c>
       <c r="R12" t="n">
-        <v>7417155</v>
+        <v>7417012</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1776,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112507843</v>
+        <v>112507895</v>
       </c>
       <c r="B13" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>740297</v>
+        <v>740295</v>
       </c>
       <c r="R13" t="n">
-        <v>7416876</v>
+        <v>7416878</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112507851</v>
+        <v>112507843</v>
       </c>
       <c r="B14" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>740502</v>
+        <v>740297</v>
       </c>
       <c r="R14" t="n">
-        <v>7417176</v>
+        <v>7416876</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1985,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hane</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112507854</v>
+        <v>112507859</v>
       </c>
       <c r="B15" t="n">
-        <v>56529</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>740450</v>
+        <v>740383</v>
       </c>
       <c r="R15" t="n">
-        <v>7417047</v>
+        <v>7416928</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2092,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112507859</v>
+        <v>112507889</v>
       </c>
       <c r="B16" t="n">
-        <v>78743</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>740383</v>
+        <v>740423</v>
       </c>
       <c r="R16" t="n">
-        <v>7416928</v>
+        <v>7416883</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112507478</v>
+        <v>112507912</v>
       </c>
       <c r="B17" t="n">
-        <v>56529</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>740495</v>
+        <v>740251</v>
       </c>
       <c r="R17" t="n">
-        <v>7417159</v>
+        <v>7416872</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2315,44 +2215,39 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112507439</v>
+        <v>112507478</v>
       </c>
       <c r="B18" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2367,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>740251</v>
+        <v>740495</v>
       </c>
       <c r="R18" t="n">
-        <v>7416907</v>
+        <v>7417159</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112507889</v>
+        <v>112507853</v>
       </c>
       <c r="B19" t="n">
-        <v>78835</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>740423</v>
+        <v>740475</v>
       </c>
       <c r="R19" t="n">
-        <v>7416883</v>
+        <v>7417153</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2505,6 +2395,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,15 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112507488</v>
+        <v>112507854</v>
       </c>
       <c r="B20" t="n">
-        <v>90934</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,13 +2461,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>740479</v>
+        <v>740450</v>
       </c>
       <c r="R20" t="n">
-        <v>7417298</v>
+        <v>7417047</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2607,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,27 +2516,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112507535</v>
+        <v>112507439</v>
       </c>
       <c r="B21" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>740053</v>
+        <v>740250</v>
       </c>
       <c r="R21" t="n">
-        <v>7417140</v>
+        <v>7416907</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,15 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112507853</v>
+        <v>112507845</v>
       </c>
       <c r="B22" t="n">
-        <v>56529</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,16 +2636,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2775,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>740476</v>
+        <v>740052</v>
       </c>
       <c r="R22" t="n">
-        <v>7417153</v>
+        <v>7417155</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2815,7 +2700,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2845,12 +2730,7 @@
         <v>112507846</v>
       </c>
       <c r="B23" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2949,37 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112507878</v>
+        <v>112507847</v>
       </c>
       <c r="B24" t="n">
-        <v>95817</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>740033</v>
+        <v>740254</v>
       </c>
       <c r="R24" t="n">
-        <v>7417169</v>
+        <v>7416908</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3025,6 +2900,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3051,15 +2931,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112507462</v>
+        <v>112507460</v>
       </c>
       <c r="B25" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3091,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>740239</v>
+        <v>740355</v>
       </c>
       <c r="R25" t="n">
-        <v>7416963</v>
+        <v>7416913</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,6 +3002,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,37 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112507532</v>
+        <v>112507462</v>
       </c>
       <c r="B26" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>740544</v>
+        <v>740239</v>
       </c>
       <c r="R26" t="n">
-        <v>7417187</v>
+        <v>7416963</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,15 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112507885</v>
+        <v>112507851</v>
       </c>
       <c r="B27" t="n">
-        <v>95823</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3295,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>740265</v>
+        <v>740502</v>
       </c>
       <c r="R27" t="n">
-        <v>7416866</v>
+        <v>7417176</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3331,6 +3201,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3360,12 +3235,7 @@
         <v>112507884</v>
       </c>
       <c r="B28" t="n">
-        <v>95823</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3459,15 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112507527</v>
+        <v>112507885</v>
       </c>
       <c r="B29" t="n">
-        <v>90608</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4787</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3499,13 +3364,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>740544</v>
+        <v>740265</v>
       </c>
       <c r="R29" t="n">
-        <v>7417187</v>
+        <v>7416866</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3549,15 +3414,403 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>112507875</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Urtimjaur, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>740538</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7417227</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>112507876</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Urtimjaur, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>740259</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7416868</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>112507877</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Urtimjaur, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>740198</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7417099</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>112507878</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Urtimjaur, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>740033</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7417169</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41396-2023 artfynd.xlsx
+++ b/artfynd/A 41396-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507507</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507901</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507532</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507533</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507534</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507536</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507902</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507903</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507895</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507859</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507889</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507912</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507478</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507853</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507854</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507439</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507845</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507846</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507847</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3030,6 +3150,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507460</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3127,6 +3252,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507462</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3229,6 +3359,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507851</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3326,6 +3461,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507884</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507885</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3520,6 +3665,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507875</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3617,6 +3767,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507876</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3714,6 +3869,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507877</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3811,8 +3971,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507878</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>